--- a/E/MKTN1.xlsx
+++ b/E/MKTN1.xlsx
@@ -172,7 +172,7 @@
     <t>20000065</t>
   </si>
   <si>
-    <t>PEDULI ANAK BANGSA</t>
+    <t>PEDULI GEMA KEBAIKAN</t>
   </si>
   <si>
     <t>23</t>
